--- a/static/contracts/test_result.xlsx
+++ b/static/contracts/test_result.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12228" yWindow="732" windowWidth="10812" windowHeight="11508" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14916" yWindow="732" windowWidth="8124" windowHeight="11508" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -27,19 +27,44 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -122,24 +147,24 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -188,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -208,40 +233,56 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -797,7 +838,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AG58"/>
+  <dimension ref="A1:AH43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="12"/>
   <cols>
     <col width="2.6640625" customWidth="1" min="1" max="1"/>
@@ -809,7 +850,7 @@
     <col width="1.109375" customWidth="1" min="7" max="7"/>
     <col width="9.109375" customWidth="1" min="8" max="8"/>
     <col width="2.33203125" customWidth="1" min="9" max="9"/>
-    <col width="6.109375" customWidth="1" min="10" max="10"/>
+    <col width="8.109375" customWidth="1" min="10" max="10"/>
     <col width="0.5546875" customWidth="1" min="11" max="11"/>
     <col width="1.44140625" customWidth="1" min="12" max="12"/>
     <col width="8.33203125" customWidth="1" min="13" max="13"/>
@@ -837,1056 +878,1008 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1"/>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>采购合同</t>
         </is>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>供方：</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>上海星河供应链有限公司</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>南京南瑞继保工程技术有限公司</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="n"/>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="M3" s="9" t="n"/>
+      <c r="R3" s="9" t="inlineStr">
         <is>
           <t>合同号：</t>
         </is>
       </c>
-      <c r="V3" s="7" t="inlineStr">
-        <is>
-          <t>JL202601290042</t>
+      <c r="V3" s="11" t="inlineStr">
+        <is>
+          <t>TEST-FONT-20260331</t>
         </is>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>需方</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>俊郎电气有限公司</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="n"/>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>需方：</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>测试需方-字体校验</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="n"/>
+      <c r="R4" s="9" t="inlineStr">
         <is>
           <t>签订地点：</t>
         </is>
       </c>
-      <c r="V4" s="12" t="inlineStr">
+      <c r="V4" s="10" t="inlineStr">
         <is>
           <t>浙江乐清</t>
         </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>备注：</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>签订日期：</t>
+        </is>
+      </c>
+      <c r="V5" s="11" t="inlineStr">
+        <is>
+          <t>2026/1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.5" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>项目号：</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>PRJ-2026-031</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="n"/>
-      <c r="N5" s="8" t="n"/>
-      <c r="P5" s="8" t="n"/>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>签订日期：</t>
-        </is>
-      </c>
-      <c r="V5" s="7" t="inlineStr">
-        <is>
-          <t>2026/1/29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25.5" customHeight="1">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>项目号：</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>2512-025A,</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="33.75" customHeight="1">
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>项目号</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="I7" s="24" t="n"/>
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>物料名称</t>
         </is>
       </c>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="19" t="n"/>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="K7" s="24" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t>物料型号规格</t>
         </is>
       </c>
-      <c r="N7" s="18" t="n"/>
-      <c r="O7" s="19" t="n"/>
-      <c r="P7" s="16" t="inlineStr">
+      <c r="N7" s="24" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="13" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="Q7" s="18" t="n"/>
-      <c r="R7" s="10" t="inlineStr">
+      <c r="Q7" s="24" t="n"/>
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="S7" s="19" t="n"/>
-      <c r="T7" s="10" t="inlineStr">
+      <c r="S7" s="25" t="n"/>
+      <c r="T7" s="14" t="inlineStr">
         <is>
           <t>含税单价</t>
         </is>
       </c>
-      <c r="U7" s="19" t="n"/>
-      <c r="V7" s="10" t="inlineStr">
+      <c r="U7" s="25" t="n"/>
+      <c r="V7" s="14" t="inlineStr">
         <is>
           <t>非税金额</t>
         </is>
       </c>
-      <c r="W7" s="19" t="n"/>
-      <c r="X7" s="16" t="inlineStr">
+      <c r="W7" s="25" t="n"/>
+      <c r="X7" s="13" t="inlineStr">
         <is>
           <t>税金</t>
         </is>
       </c>
-      <c r="Y7" s="18" t="n"/>
-      <c r="Z7" s="18" t="n"/>
-      <c r="AA7" s="16" t="inlineStr">
+      <c r="Y7" s="24" t="n"/>
+      <c r="Z7" s="24" t="n"/>
+      <c r="AA7" s="13" t="inlineStr">
         <is>
           <t>价税合计</t>
         </is>
       </c>
-      <c r="AB7" s="16" t="inlineStr">
+      <c r="AB7" s="13" t="inlineStr">
         <is>
           <t>交货
 日期</t>
         </is>
       </c>
-      <c r="AC7" s="18" t="n"/>
-      <c r="AD7" s="10" t="inlineStr">
+      <c r="AC7" s="24" t="n"/>
+      <c r="AD7" s="14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="AE7" s="18" t="n"/>
-      <c r="AF7" s="18" t="n"/>
-      <c r="AG7" s="19" t="n"/>
+      <c r="AE7" s="24" t="n"/>
+      <c r="AF7" s="24" t="n"/>
+      <c r="AG7" s="25" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>MAT-001</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="15" t="n">
-        <v>21600</v>
-      </c>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="26" t="n"/>
+      <c r="G8" s="26" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="27" t="n"/>
+      <c r="M8" s="16" t="inlineStr">
         <is>
           <t>（附清单）</t>
         </is>
       </c>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="21" t="n"/>
+      <c r="N8" s="26" t="n"/>
+      <c r="O8" s="27" t="n"/>
       <c r="P8" s="15" t="n"/>
-      <c r="Q8" s="20" t="n"/>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="21" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="21" t="n"/>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="21" t="n"/>
+      <c r="Q8" s="26" t="n"/>
+      <c r="R8" s="16" t="n"/>
+      <c r="S8" s="27" t="n"/>
+      <c r="T8" s="16" t="n"/>
+      <c r="U8" s="27" t="n"/>
+      <c r="V8" s="16" t="n"/>
+      <c r="W8" s="27" t="n"/>
       <c r="X8" s="15" t="n"/>
-      <c r="Y8" s="20" t="n"/>
-      <c r="Z8" s="20" t="n"/>
+      <c r="Y8" s="26" t="n"/>
+      <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="15" t="n"/>
       <c r="AB8" s="15" t="n"/>
-      <c r="AC8" s="20" t="n"/>
-      <c r="AD8" s="13" t="n"/>
-      <c r="AE8" s="20" t="n"/>
-      <c r="AF8" s="20" t="n"/>
-      <c r="AG8" s="21" t="n"/>
+      <c r="AC8" s="26" t="n"/>
+      <c r="AD8" s="16" t="n"/>
+      <c r="AE8" s="26" t="n"/>
+      <c r="AF8" s="26" t="n"/>
+      <c r="AG8" s="27" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>贰万圆整</t>
-        </is>
-      </c>
-      <c r="P9" s="14" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n"/>
-      <c r="V9" s="8" t="n"/>
-      <c r="X9" s="8" t="n"/>
-      <c r="AA9" s="14" t="inlineStr">
-        <is>
-          <t>20000.00</t>
-        </is>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>合计人民币金额(大写):</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>壹万贰仟叁佰肆拾陆圆整</t>
+        </is>
+      </c>
+      <c r="P9" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="T9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
+      <c r="AA9" s="19" t="n">
+        <v>12345.67</v>
       </c>
     </row>
     <row r="10" ht="0.75" customHeight="1">
-      <c r="A10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>MAT-003</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>49899.85</v>
-      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>采
+购
+条
+款</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1">
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>一、供方责任：供方按需方指定的品名、规格、产品要求、保质保量生产。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="1.5" customHeight="1">
-      <c r="D12" s="7" t="n"/>
+      <c r="D12" s="11" t="n"/>
     </row>
     <row r="13" ht="35.25" customHeight="1">
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">二、质量要求一：在需方正常使用条件下，产品实行三包。质保期为产品投运之日起2年，供方保证本合同产品为最新生产日期，非库存产品。         </t>
         </is>
       </c>
     </row>
     <row r="14" ht="0.75" customHeight="1">
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="11" t="n"/>
     </row>
     <row r="15" ht="32.25" customHeight="1">
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>三、质量要求二：供方所提供产品的资料.设计.检验和运输交货按照需方标准，若不符合要求或质量不合格，需方有权拒绝接收产品。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="1.5" customHeight="1">
-      <c r="D16" s="7" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="J16" s="9" t="n"/>
     </row>
     <row r="17" ht="44.25" customHeight="1">
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">四、质量要求三：供方保证向需方交付的本合同产品不存在、不侵犯任何第三方合法权益，且供方保证本合同产品符合中华人民共和国相关法律法规，若因供方提供的产品质量安全问题、安全隐患等风险而导致需方或第三方经济或商誉遭受损失时，供方应当全额赔偿。                                </t>
         </is>
       </c>
     </row>
     <row r="18" ht="31.5" customHeight="1">
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>五、交货方式：物流及快递费用、装卸搬运费用、质量问题的退换货费由供方承担。（交货地址：浙江省乐清市柳市镇长岐社区丰业路68号4号楼5楼）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32.25" customHeight="1">
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">六、货物的签收：本合同产品以物流方式发货，需方根据实际收货情况予以确认收货，签收货物行为不视为对产品质量验收合格。                                                           </t>
         </is>
       </c>
     </row>
     <row r="20" ht="43.5" customHeight="1">
-      <c r="D20" s="12" t="n">
-        <v>86500</v>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>七、售后服务：在超出保修服务期限后的每次售后服务，供方应按照最低标准收取相应的维修费用、更换零部件费用。售后服务结束后一个星期，需方确认签字，即完成本次售后服务。对超出保修期产品作出的收费维修部分有六个月保修。</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="30.75" customHeight="1">
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">八、违约责任：供方应在交货期内交付本合同产品，供方延迟交货的每日按照总货款金额的0.5%扣除货款，除支付违约金外，需方有权解除合同，供方收取的预付款或价款应全额返还。                                                                                </t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">九、结算方式：货到票到六个月内结清（发票需和合同内容一致）。     </t>
         </is>
       </c>
     </row>
     <row r="23" ht="30.75" customHeight="1">
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>十、合同争议的解决方式：本合同在履行过程中发生争议，有双方当事人协商解决，也可由当地工商行政管理部门协商，协商或者协商不成的，依法向人民法院起诉。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>十一、本合同自需供方签字盖章后生效（传真有效）受相关法律法规制约。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20.25" customHeight="1">
-      <c r="D25" s="7" t="inlineStr">
+    <row r="25" ht="19.8" customHeight="1">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>十二、逾期未交货按照每日按照总货款金额的0.5%扣除货款。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>供
-方</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+    <row r="26" ht="16.05" customHeight="1">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>供方</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>单位名称：</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>南京南瑞继保工程技术有限公司</t>
         </is>
       </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t>需
-方</t>
-        </is>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
+      <c r="R26" s="22" t="inlineStr">
+        <is>
+          <t>需方</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
         <is>
           <t>单位名称：</t>
         </is>
       </c>
-      <c r="X26" s="7" t="inlineStr">
-        <is>
-          <t>俊郎电气有限公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="0.75" customHeight="1"/>
-    <row r="28" ht="0.75" customHeight="1">
-      <c r="X28" s="7" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>俊朗电气有限公司</t>
+        </is>
+      </c>
+      <c r="AF26" s="8" t="n"/>
+      <c r="AG26" s="8" t="n"/>
+      <c r="AH26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="16.05" customHeight="1">
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>地址：</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="n"/>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>地址：</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>乐清柳市镇象阳工业区</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="0.75" customHeight="1"/>
-    <row r="30" ht="12.75" customHeight="1">
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>地址：</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>地址：</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="3.75" customHeight="1">
-      <c r="X31" s="7" t="inlineStr">
+      <c r="AF27" s="7" t="n"/>
+      <c r="AG27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="16.05" customHeight="1">
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>法定代理人：</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="n"/>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>法定代理人：</t>
+        </is>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>李志雄</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="11.25" customHeight="1">
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>法定代表人：</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>法定代表人：</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="4.5" customHeight="1">
-      <c r="X33" s="7" t="inlineStr">
+      <c r="AF28" s="7" t="n"/>
+      <c r="AG28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="16.05" customHeight="1">
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>委托代理人：</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="n"/>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>委托代理人：</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>许梦雨</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="9.75" customHeight="1">
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>委托代理人：</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="T34" s="7" t="inlineStr">
-        <is>
-          <t>委托代理人：</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="6.75" customHeight="1"/>
-    <row r="36" ht="8.25" customHeight="1">
-      <c r="D36" s="7" t="inlineStr">
+      <c r="AF29" s="7" t="n"/>
+      <c r="AG29" s="7" t="n"/>
+    </row>
+    <row r="30" ht="16.05" customHeight="1">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>联系电话：</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T36" s="7" t="inlineStr">
+      <c r="I30" s="11" t="n"/>
+      <c r="T30" s="11" t="inlineStr">
         <is>
           <t>联系电话：</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="8.25" customHeight="1">
-      <c r="X37" s="7" t="inlineStr">
+      <c r="W30" s="11" t="n"/>
+      <c r="AF30" s="7" t="n"/>
+      <c r="AG30" s="7" t="n"/>
+    </row>
+    <row r="31" ht="16.05" customHeight="1">
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>开户银行：</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>交通银行南京新街口支行</t>
+        </is>
+      </c>
+      <c r="T31" s="11" t="inlineStr">
+        <is>
+          <t>开户银行：</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>建设银行乐清柳市支行</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="6" customHeight="1">
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>开户银行：</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>交通银行南京新街口支行</t>
-        </is>
-      </c>
-      <c r="T38" s="7" t="inlineStr">
-        <is>
-          <t>开户银行：</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="9.75" customHeight="1">
-      <c r="X39" s="7" t="inlineStr">
+      <c r="AF31" s="7" t="n"/>
+      <c r="AG31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="16.05" customHeight="1">
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>账号：</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>320006607010141108411</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr">
+        <is>
+          <t>账号：</t>
+        </is>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>33001627564053011062</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="4.5" customHeight="1">
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>账    号：</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>320006607010141108411</t>
-        </is>
-      </c>
-      <c r="T40" s="7" t="inlineStr">
-        <is>
-          <t>账    号：</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="12.75" customHeight="1">
-      <c r="X41" s="7" t="inlineStr">
+      <c r="AF32" s="7" t="n"/>
+      <c r="AG32" s="7" t="n"/>
+    </row>
+    <row r="33" ht="16.05" customHeight="1">
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>税号：</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="n"/>
+      <c r="T33" s="11" t="inlineStr">
+        <is>
+          <t>税号：</t>
+        </is>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>91330382695265936J</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="1.5" customHeight="1">
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>税    号：</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T42" s="7" t="inlineStr">
-        <is>
-          <t>税    号：</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1">
-      <c r="X43" s="7" t="inlineStr">
+      <c r="AF33" s="7" t="n"/>
+      <c r="AG33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="16.05" customHeight="1">
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>传真：</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="n"/>
+      <c r="T34" s="11" t="inlineStr">
+        <is>
+          <t>传真：</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>057761616635</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="0.75" customHeight="1">
-      <c r="X44" s="7" t="inlineStr">
+      <c r="AF34" s="7" t="n"/>
+      <c r="AG34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="16.05" customHeight="1">
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>邮编：</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="n"/>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>邮编：</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>710018</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="9" customHeight="1">
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>传    真：</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T45" s="7" t="inlineStr">
-        <is>
-          <t>传    真：</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="4.5" customHeight="1"/>
-    <row r="47" ht="3" customHeight="1"/>
-    <row r="48" ht="15" customHeight="1">
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>邮    编：</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="T48" s="7" t="inlineStr">
-        <is>
-          <t>邮    编：</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="0.75" customHeight="1"/>
-    <row r="50" ht="36.75" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1">
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="K51" s="11" t="n"/>
-      <c r="O51" s="11" t="n"/>
-      <c r="Q51" s="11" t="n"/>
-      <c r="S51" s="11" t="n"/>
-      <c r="U51" s="11" t="n"/>
-      <c r="W51" s="11" t="n"/>
-      <c r="Z51" s="11" t="n"/>
-      <c r="AC51" s="11" t="n"/>
-      <c r="AF51" s="11" t="n"/>
-    </row>
-    <row r="52" ht="14.25" customHeight="1">
-      <c r="B52" s="11" t="n"/>
-      <c r="C52" s="11" t="n"/>
-      <c r="G52" s="11" t="n"/>
-      <c r="I52" s="11" t="n"/>
-      <c r="K52" s="11" t="n"/>
-      <c r="O52" s="11" t="n"/>
-      <c r="Q52" s="11" t="n"/>
-      <c r="S52" s="11" t="n"/>
-      <c r="U52" s="11" t="n"/>
-      <c r="W52" s="11" t="n"/>
-      <c r="Z52" s="11" t="n"/>
-      <c r="AC52" s="11" t="n"/>
-      <c r="AF52" s="11" t="n"/>
-    </row>
-    <row r="53" ht="14.25" customHeight="1">
-      <c r="B53" s="11" t="n"/>
-      <c r="C53" s="11" t="n"/>
-      <c r="G53" s="11" t="n"/>
-      <c r="I53" s="11" t="n"/>
-      <c r="K53" s="11" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="Q53" s="11" t="n"/>
-      <c r="S53" s="11" t="n"/>
-      <c r="U53" s="11" t="n"/>
-      <c r="W53" s="11" t="n"/>
-      <c r="Z53" s="11" t="n"/>
-      <c r="AC53" s="11" t="n"/>
-      <c r="AF53" s="11" t="n"/>
-    </row>
-    <row r="54" ht="24.75" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1">
-      <c r="B55" s="11" t="n"/>
-      <c r="C55" s="11" t="n"/>
-      <c r="G55" s="11" t="n"/>
-      <c r="I55" s="11" t="n"/>
-      <c r="K55" s="11" t="n"/>
-      <c r="O55" s="11" t="n"/>
-      <c r="Q55" s="11" t="n"/>
-      <c r="S55" s="11" t="n"/>
-      <c r="U55" s="11" t="n"/>
-      <c r="W55" s="11" t="n"/>
-      <c r="Z55" s="11" t="n"/>
-      <c r="AC55" s="11" t="n"/>
-      <c r="AF55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="27" customHeight="1">
-      <c r="B56" s="10" t="inlineStr">
+      <c r="AF35" s="7" t="n"/>
+      <c r="AG35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="16.05" customHeight="1">
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="O36" s="18" t="n"/>
+      <c r="Q36" s="18" t="n"/>
+      <c r="S36" s="18" t="n"/>
+      <c r="U36" s="18" t="n"/>
+      <c r="W36" s="18" t="n"/>
+      <c r="Z36" s="18" t="n"/>
+      <c r="AC36" s="18" t="n"/>
+      <c r="AF36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="Q37" s="18" t="n"/>
+      <c r="S37" s="18" t="n"/>
+      <c r="U37" s="18" t="n"/>
+      <c r="W37" s="18" t="n"/>
+      <c r="Z37" s="18" t="n"/>
+      <c r="AC37" s="18" t="n"/>
+      <c r="AF37" s="18" t="n"/>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+      <c r="Q38" s="18" t="n"/>
+      <c r="S38" s="18" t="n"/>
+      <c r="U38" s="18" t="n"/>
+      <c r="W38" s="18" t="n"/>
+      <c r="Z38" s="18" t="n"/>
+      <c r="AC38" s="18" t="n"/>
+      <c r="AF38" s="18" t="n"/>
+    </row>
+    <row r="39" ht="24.75" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="K40" s="18" t="n"/>
+      <c r="O40" s="18" t="n"/>
+      <c r="Q40" s="18" t="n"/>
+      <c r="S40" s="18" t="n"/>
+      <c r="U40" s="18" t="n"/>
+      <c r="W40" s="18" t="n"/>
+      <c r="Z40" s="18" t="n"/>
+      <c r="AC40" s="18" t="n"/>
+      <c r="AF40" s="18" t="n"/>
+    </row>
+    <row r="41" ht="27" customHeight="1">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>项目号</t>
         </is>
       </c>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="18" t="n"/>
-      <c r="F56" s="19" t="n"/>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="24" t="n"/>
+      <c r="F41" s="25" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="H56" s="19" t="n"/>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="J56" s="19" t="n"/>
-      <c r="K56" s="10" t="inlineStr">
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="14" t="inlineStr">
         <is>
           <t>物料型号规格</t>
         </is>
       </c>
-      <c r="L56" s="18" t="n"/>
-      <c r="M56" s="18" t="n"/>
-      <c r="N56" s="19" t="n"/>
-      <c r="O56" s="10" t="inlineStr">
+      <c r="L41" s="24" t="n"/>
+      <c r="M41" s="24" t="n"/>
+      <c r="N41" s="25" t="n"/>
+      <c r="O41" s="14" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="P56" s="19" t="n"/>
-      <c r="Q56" s="10" t="inlineStr">
+      <c r="P41" s="25" t="n"/>
+      <c r="Q41" s="14" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="R56" s="19" t="n"/>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="R41" s="25" t="n"/>
+      <c r="S41" s="14" t="inlineStr">
         <is>
           <t>含税单价</t>
         </is>
       </c>
-      <c r="T56" s="19" t="n"/>
-      <c r="U56" s="10" t="inlineStr">
+      <c r="T41" s="25" t="n"/>
+      <c r="U41" s="14" t="inlineStr">
         <is>
           <t>非税金额</t>
         </is>
       </c>
-      <c r="V56" s="19" t="n"/>
-      <c r="W56" s="10" t="inlineStr">
+      <c r="V41" s="25" t="n"/>
+      <c r="W41" s="14" t="inlineStr">
         <is>
           <t>税金</t>
         </is>
       </c>
-      <c r="X56" s="18" t="n"/>
-      <c r="Y56" s="19" t="n"/>
-      <c r="Z56" s="10" t="inlineStr">
+      <c r="X41" s="24" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="14" t="inlineStr">
         <is>
           <t>价税合计</t>
         </is>
       </c>
-      <c r="AA56" s="18" t="n"/>
-      <c r="AB56" s="19" t="n"/>
-      <c r="AC56" s="10" t="inlineStr">
+      <c r="AA41" s="24" t="n"/>
+      <c r="AB41" s="25" t="n"/>
+      <c r="AC41" s="14" t="inlineStr">
         <is>
           <t>交货
 日期</t>
         </is>
       </c>
-      <c r="AD56" s="18" t="n"/>
-      <c r="AE56" s="18" t="n"/>
-      <c r="AF56" s="18" t="n"/>
-      <c r="AG56" s="19" t="n"/>
-    </row>
-    <row r="57" ht="57.75" customHeight="1">
-      <c r="B57" s="9" t="inlineStr">
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="24" t="n"/>
+      <c r="AF41" s="24" t="n"/>
+      <c r="AG41" s="25" t="n"/>
+    </row>
+    <row r="42" ht="57.75" customHeight="1">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>2512-025A</t>
         </is>
       </c>
-      <c r="D57" s="18" t="n"/>
-      <c r="E57" s="18" t="n"/>
-      <c r="F57" s="19" t="n"/>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="D42" s="24" t="n"/>
+      <c r="E42" s="24" t="n"/>
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="21" t="inlineStr">
         <is>
           <t>赢联盟几内亚项目箱变WCIE-WCSR-几内亚共和国-</t>
         </is>
       </c>
-      <c r="H57" s="19" t="n"/>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="21" t="inlineStr">
         <is>
           <t>微机保护装置</t>
         </is>
       </c>
-      <c r="J57" s="19" t="n"/>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="21" t="inlineStr">
         <is>
           <t>PCS-9611S-S</t>
         </is>
       </c>
-      <c r="L57" s="18" t="n"/>
-      <c r="M57" s="18" t="n"/>
-      <c r="N57" s="19" t="n"/>
-      <c r="O57" s="9" t="inlineStr">
+      <c r="L42" s="24" t="n"/>
+      <c r="M42" s="24" t="n"/>
+      <c r="N42" s="25" t="n"/>
+      <c r="O42" s="21" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="P57" s="19" t="n"/>
-      <c r="Q57" s="9" t="inlineStr">
+      <c r="P42" s="25" t="n"/>
+      <c r="Q42" s="21" t="inlineStr">
         <is>
           <t>只</t>
         </is>
       </c>
-      <c r="R57" s="19" t="n"/>
-      <c r="S57" s="9" t="inlineStr">
+      <c r="R42" s="25" t="n"/>
+      <c r="S42" s="21" t="inlineStr">
         <is>
           <t>20000.00</t>
         </is>
       </c>
-      <c r="T57" s="19" t="n"/>
-      <c r="U57" s="9" t="inlineStr">
+      <c r="T42" s="25" t="n"/>
+      <c r="U42" s="21" t="inlineStr">
         <is>
           <t>17699.12</t>
         </is>
       </c>
-      <c r="V57" s="19" t="n"/>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="V42" s="25" t="n"/>
+      <c r="W42" s="21" t="inlineStr">
         <is>
           <t>2300.88</t>
         </is>
       </c>
-      <c r="X57" s="18" t="n"/>
-      <c r="Y57" s="19" t="n"/>
-      <c r="Z57" s="9" t="inlineStr">
+      <c r="X42" s="24" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="21" t="inlineStr">
         <is>
           <t>20000.00</t>
         </is>
       </c>
-      <c r="AA57" s="18" t="n"/>
-      <c r="AB57" s="19" t="n"/>
-      <c r="AC57" s="9" t="inlineStr">
+      <c r="AA42" s="24" t="n"/>
+      <c r="AB42" s="25" t="n"/>
+      <c r="AC42" s="21" t="inlineStr">
         <is>
           <t>2026-1-16</t>
         </is>
       </c>
-      <c r="AD57" s="18" t="n"/>
-      <c r="AE57" s="18" t="n"/>
-      <c r="AF57" s="18" t="n"/>
-      <c r="AG57" s="19" t="n"/>
-    </row>
-    <row r="58" ht="39.75" customHeight="1">
-      <c r="B58" s="9" t="inlineStr">
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="24" t="n"/>
+      <c r="AF42" s="24" t="n"/>
+      <c r="AG42" s="25" t="n"/>
+    </row>
+    <row r="43" ht="39.75" customHeight="1">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>备注：南瑞 发施耐德</t>
         </is>
       </c>
-      <c r="C58" s="18" t="n"/>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="18" t="n"/>
-      <c r="I58" s="18" t="n"/>
-      <c r="J58" s="18" t="n"/>
-      <c r="K58" s="18" t="n"/>
-      <c r="L58" s="18" t="n"/>
-      <c r="M58" s="18" t="n"/>
-      <c r="N58" s="18" t="n"/>
-      <c r="O58" s="18" t="n"/>
-      <c r="P58" s="18" t="n"/>
-      <c r="Q58" s="18" t="n"/>
-      <c r="R58" s="18" t="n"/>
-      <c r="S58" s="18" t="n"/>
-      <c r="T58" s="18" t="n"/>
-      <c r="U58" s="18" t="n"/>
-      <c r="V58" s="18" t="n"/>
-      <c r="W58" s="18" t="n"/>
-      <c r="X58" s="18" t="n"/>
-      <c r="Y58" s="18" t="n"/>
-      <c r="Z58" s="18" t="n"/>
-      <c r="AA58" s="18" t="n"/>
-      <c r="AB58" s="18" t="n"/>
-      <c r="AC58" s="18" t="n"/>
-      <c r="AD58" s="18" t="n"/>
-      <c r="AE58" s="18" t="n"/>
-      <c r="AF58" s="18" t="n"/>
-      <c r="AG58" s="19" t="n"/>
+      <c r="C43" s="24" t="n"/>
+      <c r="D43" s="24" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="24" t="n"/>
+      <c r="G43" s="24" t="n"/>
+      <c r="H43" s="24" t="n"/>
+      <c r="I43" s="24" t="n"/>
+      <c r="J43" s="24" t="n"/>
+      <c r="K43" s="24" t="n"/>
+      <c r="L43" s="24" t="n"/>
+      <c r="M43" s="24" t="n"/>
+      <c r="N43" s="24" t="n"/>
+      <c r="O43" s="24" t="n"/>
+      <c r="P43" s="24" t="n"/>
+      <c r="Q43" s="24" t="n"/>
+      <c r="R43" s="24" t="n"/>
+      <c r="S43" s="24" t="n"/>
+      <c r="T43" s="24" t="n"/>
+      <c r="U43" s="24" t="n"/>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="24" t="n"/>
+      <c r="X43" s="24" t="n"/>
+      <c r="Y43" s="24" t="n"/>
+      <c r="Z43" s="24" t="n"/>
+      <c r="AA43" s="24" t="n"/>
+      <c r="AB43" s="24" t="n"/>
+      <c r="AC43" s="24" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="24" t="n"/>
+      <c r="AF43" s="24" t="n"/>
+      <c r="AG43" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="180">
+  <mergeCells count="181">
     <mergeCell ref="R3:U3"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="AC53:AE53"/>
-    <mergeCell ref="D40:G41"/>
-    <mergeCell ref="T26:W28"/>
+    <mergeCell ref="W26:AE26"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="F33:H33"/>
     <mergeCell ref="D8:G8"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="T38:W39"/>
     <mergeCell ref="D11:AG11"/>
-    <mergeCell ref="X44:AG46"/>
-    <mergeCell ref="AC55:AE55"/>
+    <mergeCell ref="K38:N38"/>
     <mergeCell ref="D16:I16"/>
-    <mergeCell ref="D42:G44"/>
-    <mergeCell ref="Q55:R55"/>
-    <mergeCell ref="T40:W41"/>
-    <mergeCell ref="D26:G28"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="AC38:AE38"/>
+    <mergeCell ref="F31:H31"/>
     <mergeCell ref="E3:K3"/>
-    <mergeCell ref="Q51:R51"/>
-    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="J16:AG16"/>
+    <mergeCell ref="T31:V31"/>
+    <mergeCell ref="O41:P41"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="S57:T57"/>
-    <mergeCell ref="U57:V57"/>
-    <mergeCell ref="AF55:AG55"/>
-    <mergeCell ref="O55:P55"/>
-    <mergeCell ref="W57:Y57"/>
+    <mergeCell ref="R26:S35"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="T28:V28"/>
+    <mergeCell ref="I42:J42"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="O40:P40"/>
     <mergeCell ref="D15:AG15"/>
+    <mergeCell ref="W28:AE28"/>
     <mergeCell ref="D24:AG24"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="W53:Y53"/>
-    <mergeCell ref="Z55:AB55"/>
-    <mergeCell ref="D45:G47"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="T30:V30"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="I30:Q30"/>
+    <mergeCell ref="AF40:AG40"/>
     <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="D30:G31"/>
+    <mergeCell ref="T29:V29"/>
     <mergeCell ref="T7:U7"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="AC56:AG56"/>
-    <mergeCell ref="X31:AG32"/>
-    <mergeCell ref="H30:Q31"/>
-    <mergeCell ref="T32:W33"/>
+    <mergeCell ref="AF38:AG38"/>
     <mergeCell ref="D7:G7"/>
+    <mergeCell ref="W36:Y36"/>
     <mergeCell ref="D10:AG10"/>
     <mergeCell ref="V4:AG4"/>
     <mergeCell ref="X7:Z7"/>
-    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="AC41:AG41"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="R8:S8"/>
-    <mergeCell ref="T48:W49"/>
-    <mergeCell ref="T30:W31"/>
-    <mergeCell ref="K53:N53"/>
-    <mergeCell ref="Z56:AB56"/>
+    <mergeCell ref="I32:Q32"/>
+    <mergeCell ref="AF37:AG37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="W32:AE32"/>
     <mergeCell ref="AD7:AG7"/>
-    <mergeCell ref="AC57:AG57"/>
     <mergeCell ref="V8:W8"/>
-    <mergeCell ref="Q52:R52"/>
-    <mergeCell ref="S52:T52"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="G40:H40"/>
     <mergeCell ref="H9:O9"/>
+    <mergeCell ref="K37:N37"/>
     <mergeCell ref="J7:L7"/>
-    <mergeCell ref="I57:J57"/>
     <mergeCell ref="D17:AG17"/>
-    <mergeCell ref="Z51:AB51"/>
-    <mergeCell ref="AF53:AG53"/>
-    <mergeCell ref="D48:G49"/>
-    <mergeCell ref="H34:Q35"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I33:Q33"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="B43:AG43"/>
+    <mergeCell ref="S38:T38"/>
     <mergeCell ref="AD8:AG8"/>
-    <mergeCell ref="B58:AG58"/>
-    <mergeCell ref="H42:Q44"/>
+    <mergeCell ref="W27:AE27"/>
+    <mergeCell ref="U41:V41"/>
     <mergeCell ref="T9:U9"/>
     <mergeCell ref="V9:W9"/>
-    <mergeCell ref="X33:AG34"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="H36:Q37"/>
+    <mergeCell ref="I35:Q35"/>
     <mergeCell ref="B2:AG2"/>
-    <mergeCell ref="R26:S48"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="AC42:AG42"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="AC51:AE51"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="W38:Y38"/>
     <mergeCell ref="D12:AG12"/>
-    <mergeCell ref="U56:V56"/>
     <mergeCell ref="D25:AG25"/>
     <mergeCell ref="P9:S9"/>
     <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="O51:P51"/>
     <mergeCell ref="AA9:AG9"/>
-    <mergeCell ref="K51:N51"/>
-    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Z36:AB36"/>
+    <mergeCell ref="W40:Y40"/>
+    <mergeCell ref="F29:H29"/>
     <mergeCell ref="D14:AG14"/>
+    <mergeCell ref="K41:N41"/>
     <mergeCell ref="V3:AG3"/>
-    <mergeCell ref="T34:W35"/>
     <mergeCell ref="D23:AG23"/>
-    <mergeCell ref="X28:AG30"/>
-    <mergeCell ref="K56:N56"/>
-    <mergeCell ref="H45:Q47"/>
+    <mergeCell ref="W34:AE34"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="T32:V32"/>
     <mergeCell ref="V5:AG5"/>
-    <mergeCell ref="H48:Q49"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="O57:P57"/>
-    <mergeCell ref="Q57:R57"/>
-    <mergeCell ref="S51:T51"/>
+    <mergeCell ref="D26:E35"/>
+    <mergeCell ref="W30:AE30"/>
+    <mergeCell ref="K42:N42"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="X39:AG40"/>
+    <mergeCell ref="G42:H42"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="H38:Q39"/>
-    <mergeCell ref="X26:AG26"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="D32:G33"/>
-    <mergeCell ref="H40:Q41"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="W31:AE31"/>
+    <mergeCell ref="O36:P36"/>
     <mergeCell ref="E4:L4"/>
-    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="Z38:AB38"/>
     <mergeCell ref="R7:S7"/>
-    <mergeCell ref="X43:AG43"/>
-    <mergeCell ref="W52:Y52"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="U37:V37"/>
     <mergeCell ref="D18:AG18"/>
-    <mergeCell ref="T45:W47"/>
-    <mergeCell ref="H26:Q28"/>
-    <mergeCell ref="K55:N55"/>
-    <mergeCell ref="S53:T53"/>
-    <mergeCell ref="AC52:AE52"/>
+    <mergeCell ref="T27:V27"/>
+    <mergeCell ref="W37:Y37"/>
     <mergeCell ref="B10:C25"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="M3:Q3"/>
-    <mergeCell ref="X41:AG42"/>
-    <mergeCell ref="S55:T55"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="U55:V55"/>
-    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="I34:Q34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="AC37:AE37"/>
     <mergeCell ref="D20:AG20"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="Z57:AB57"/>
-    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="W33:AE33"/>
+    <mergeCell ref="I27:Q27"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="T35:V35"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="S41:T41"/>
     <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="B26:C48"/>
-    <mergeCell ref="T36:W37"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="W51:Y51"/>
+    <mergeCell ref="D22:AG22"/>
+    <mergeCell ref="W35:AE35"/>
     <mergeCell ref="M4:Q4"/>
-    <mergeCell ref="D22:AG22"/>
-    <mergeCell ref="Q56:R56"/>
-    <mergeCell ref="S56:T56"/>
-    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="W41:Y41"/>
+    <mergeCell ref="Z37:AB37"/>
     <mergeCell ref="D21:AG21"/>
+    <mergeCell ref="I28:Q28"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G36:H36"/>
     <mergeCell ref="D13:AG13"/>
     <mergeCell ref="M7:O7"/>
-    <mergeCell ref="Z52:AB52"/>
+    <mergeCell ref="I36:J36"/>
     <mergeCell ref="E5:L5"/>
-    <mergeCell ref="W56:Y56"/>
-    <mergeCell ref="K57:N57"/>
-    <mergeCell ref="D36:G37"/>
     <mergeCell ref="R5:U5"/>
-    <mergeCell ref="X37:AG38"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="W42:Y42"/>
     <mergeCell ref="M8:O8"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="T42:W44"/>
+    <mergeCell ref="C42:F42"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="I29:Q29"/>
+    <mergeCell ref="K36:N36"/>
     <mergeCell ref="R4:U4"/>
     <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="W29:AE29"/>
+    <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="AF51:AG51"/>
+    <mergeCell ref="Z40:AB40"/>
     <mergeCell ref="F6:AG6"/>
-    <mergeCell ref="H32:Q33"/>
-    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="I31:Q31"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="S36:T36"/>
     <mergeCell ref="AB8:AC8"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="G55:H55"/>
     <mergeCell ref="V7:W7"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="D38:G39"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="U38:V38"/>
     <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="AF52:AG52"/>
     <mergeCell ref="D19:AG19"/>
+    <mergeCell ref="I26:Q26"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="D34:G35"/>
-    <mergeCell ref="W55:Y55"/>
+    <mergeCell ref="O37:P37"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="AF36:AG36"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" errors="blank"/>

--- a/static/contracts/test_result.xlsx
+++ b/static/contracts/test_result.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="V3" s="11" t="inlineStr">
         <is>
-          <t>TEST-FONT-20260331</t>
+          <t>TEST-SUP-20260331</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>测试需方-字体校验</t>
+          <t>俊朗电气有限公司</t>
         </is>
       </c>
       <c r="M4" s="9" t="n"/>
@@ -1112,10 +1112,7 @@
     <row r="10" ht="0.75" customHeight="1">
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>采
-购
-条
-款</t>
+          <t>6222000012345678</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -1215,6 +1212,11 @@
       </c>
     </row>
     <row r="26" ht="16.05" customHeight="1">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>91310000XXXXXXX</t>
+        </is>
+      </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
           <t>供方</t>
